--- a/output/pdf_financials_xlsx/SWAN.xlsx
+++ b/output/pdf_financials_xlsx/SWAN.xlsx
@@ -5402,31 +5402,31 @@
         <v>0.055735</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.055735</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.055735</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.055735</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.055735</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.055735</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.055735</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.055735</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.055735</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.055735</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0.390128</v>
@@ -6712,7 +6712,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0247</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0.028398</v>
@@ -10851,7 +10851,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -11735,7 +11739,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -12176,7 +12184,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -13450,7 +13462,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>0.04519</v>
       </c>
@@ -20695,7 +20711,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SWAN.xlsx
+++ b/output/pdf_financials_xlsx/SWAN.xlsx
@@ -888,10 +888,10 @@
         <v>0.000235</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.035008</v>
+        <v>0.052072</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.035784</v>
+        <v>0.067575</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.203558</v>
@@ -903,22 +903,22 @@
         <v>0.163347</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.117835</v>
+        <v>0.189106</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.028121</v>
+        <v>0.058026</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.027694</v>
+        <v>0.061961</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.166603</v>
+        <v>0.246046</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.102062</v>
+        <v>0.200671</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.131985</v>
+        <v>0.229823</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>1.381668</v>
@@ -965,22 +965,22 @@
         <v>-0.163347</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.117835</v>
+        <v>-0.189106</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.028121</v>
+        <v>-0.058026</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.027694</v>
+        <v>-0.061961</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.166603</v>
+        <v>-0.246046</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.102062</v>
+        <v>-0.200671</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.131985</v>
+        <v>-0.229823</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>-1.381668</v>
@@ -1029,19 +1029,19 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.009419</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.004537</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.024454</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.146301</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.124936</v>
       </c>
     </row>
     <row r="13">
@@ -1879,19 +1879,19 @@
         <v>-0.246046</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.191252</v>
+        <v>-0.200671</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.940819</v>
+        <v>-1.945356</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-8.491318</v>
+        <v>-8.466863999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-6.084702</v>
+        <v>-5.938401</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.393895</v>
+        <v>-3.268959</v>
       </c>
     </row>
     <row r="28">
@@ -1983,19 +1983,19 @@
         <v>-0.246046</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.191252</v>
+        <v>-0.200671</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.940819</v>
+        <v>-1.945356</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-8.491318</v>
+        <v>-8.466863999999999</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-6.084702</v>
+        <v>-5.938401</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.393895</v>
+        <v>-3.268959</v>
       </c>
     </row>
     <row r="30">
@@ -2228,40 +2228,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.299765</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.383391</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.249465</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.065024</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.019255</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.00113</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000374</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000126</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.5259200000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.291596</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.011433</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.89962</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>8.874656999999999</v>
@@ -2332,40 +2332,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.299765</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.383391</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.249465</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.065024</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.019255</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.00113</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000374</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000126</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.5259200000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.291596</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.011433</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.89962</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>8.874656999999999</v>
@@ -2962,13 +2962,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.321332</v>
+        <v>0.071867</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.128916</v>
+        <v>0.063892</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.053205</v>
+        <v>0.03395</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.906355</v>
+        <v>0.006735</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.000626</v>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -22980,7 +22980,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -26904,7 +26904,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -27068,7 +27068,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">

--- a/output/pdf_financials_xlsx/SWAN.xlsx
+++ b/output/pdf_financials_xlsx/SWAN.xlsx
@@ -1934,16 +1934,16 @@
         <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.315312</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.94593</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.945928</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.945928</v>
       </c>
     </row>
     <row r="29">
@@ -1986,16 +1986,16 @@
         <v>-0.200671</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.945356</v>
+        <v>-1.630044</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-8.466863999999999</v>
+        <v>-7.520934</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.938401</v>
+        <v>-4.992473</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.268959</v>
+        <v>-2.323031</v>
       </c>
     </row>
     <row r="30">
@@ -22371,7 +22371,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -25476,7 +25476,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">

--- a/output/pdf_financials_xlsx/SWAN.xlsx
+++ b/output/pdf_financials_xlsx/SWAN.xlsx
@@ -17365,7 +17365,11 @@
           <t>Payment of share issue costs related to private placement</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -21085,7 +21089,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E150" s="5" t="n">
         <v>0.3</v>
       </c>
